--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>נגה ארז Stuck In Heaven</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a4%d7%9c%d7%9c%d7%95-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר יושב היטב בתוך העולם הסגנוני של קובי אפללו – בלדה רכה, רגשית, עם דגש על אינטימיות, זיכרון וזוגיות מתמשכת. השיר עוסק בכמה נושאים מרכזיים: אהבה מתמשכת לאורך שנים, התמודדות עם קשיים (“כשהכאב נגע…”), זיכרון ככוח מחזק, יצירה משותפת של</v>
+        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>נגה ארז Stuck In Heaven</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
+        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
+        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
+        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>החצר האחורית של ג'וני לבד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
+        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%a9%d7%9c-%d7%92%d7%95%d7%a0%d7%99-%d7%9c%d7%91%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-30</v>
+        <v>2026-03-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
+        <v>השיר לבד של יונתן כהן (מהפרויקט “החצר האחורית של ג’וני”) הוא שיר חשוף, כמעט כמו מונולוג אישי—שנע בין סיפור חיים, וידוי נפשי וביקורת חברתית, עטוף בסאונד ים־תיכוני עם נגיעות היפ־הופ. השורה: “עברתי את מסע החיים הרבה לפני משבר 40” היא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>החצר האחורית של ג'וני לבד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week05/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
     </row>
   </sheetData>
